--- a/Analysis/03_Hypothesis_Tests/2_strategic_classification_table.xlsx
+++ b/Analysis/03_Hypothesis_Tests/2_strategic_classification_table.xlsx
@@ -687,7 +687,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Emerging Leverage Sectors</t>
+          <t>Peripheral Limited-Impact Sectors</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="H33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Structurally Critical but Low-Transmission Sectors</t>
+          <t>Strategic Core Sectors</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Emerging Leverage Sectors</t>
+          <t>Peripheral Limited-Impact Sectors</t>
         </is>
       </c>
       <c r="H61" t="b">
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3151799450364158</v>
+        <v>0.3107854770460811</v>
       </c>
     </row>
     <row r="4">
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2650606464422767</v>
+        <v>0.267864088198806</v>
       </c>
     </row>
     <row r="6">
